--- a/Teams.xlsx
+++ b/Teams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\UST\Batch_29Oct25\all\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{77B502BC-A3D5-4777-B432-BC7D1F3054F7}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F98580A8-AADC-4E08-B40C-EDE9B3F48F1F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{3D2F2C73-225E-4479-9257-01007F8BBF14}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Kanderi Reshma Sri</t>
   </si>
@@ -142,6 +142,9 @@
   </si>
   <si>
     <t>Project title</t>
+  </si>
+  <si>
+    <t>Medicare Appointment System</t>
   </si>
 </sst>
 </file>
@@ -173,7 +176,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -196,14 +199,60 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="45" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="45" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="45" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -523,7 +572,7 @@
   <cols>
     <col min="2" max="2" width="25.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.77734375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="3" bestFit="1" customWidth="1"/>
@@ -553,7 +602,9 @@
       <c r="D3" s="1">
         <v>1</v>
       </c>
-      <c r="E3" s="1"/>
+      <c r="E3" s="3" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -565,7 +616,7 @@
       <c r="D4" s="1">
         <v>1</v>
       </c>
-      <c r="E4" s="1"/>
+      <c r="E4" s="4"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
@@ -577,7 +628,7 @@
       <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="E5" s="1"/>
+      <c r="E5" s="4"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
@@ -589,7 +640,7 @@
       <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="1"/>
+      <c r="E6" s="5"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
@@ -955,6 +1006,9 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:E37">
     <sortCondition ref="D3:D37"/>
   </sortState>
+  <mergeCells count="1">
+    <mergeCell ref="E3:E6"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
